--- a/grupos/5APV - Estadisticos 20221.xlsx
+++ b/grupos/5APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="100">
   <si>
     <t>Materia</t>
   </si>
@@ -140,18 +140,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
@@ -170,151 +170,151 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
     <t>BALTAZARES</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>TINOCO</t>
   </si>
   <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
   </si>
   <si>
     <t>IVETTE</t>
   </si>
   <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>LEONARDO GAEL</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
+    <t>IAN URIEL</t>
+  </si>
+  <si>
+    <t>JESUS HUMBERTO</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>KARLA RENATA</t>
   </si>
   <si>
     <t>MIGUEL ANGEL ONAM</t>
   </si>
   <si>
-    <t>MARCO JOSAFAT</t>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>KAREN YAZMIN</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
+    <t>AXEL YAEL</t>
   </si>
   <si>
     <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>AXEL YAEL</t>
   </si>
   <si>
     <t>URIEL ALFREDO</t>
@@ -815,28 +815,28 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -857,10 +857,10 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -869,10 +869,10 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -898,22 +898,22 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -934,10 +934,10 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -960,7 +960,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>-1</v>
@@ -975,7 +975,7 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -984,13 +984,13 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1011,10 +1011,10 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1037,7 +1037,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>-1</v>
@@ -1052,10 +1052,10 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1064,10 +1064,10 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1091,7 +1091,7 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1129,22 +1129,22 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1165,10 +1165,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1177,10 +1177,10 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1206,22 +1206,22 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1242,7 +1242,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1254,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1283,22 +1283,22 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1319,16 +1319,16 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1354,28 +1354,28 @@
         <v>8</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G11">
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1396,7 +1396,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1408,7 +1408,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1422,7 +1422,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>-1</v>
@@ -1434,7 +1434,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1443,7 +1443,7 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1464,10 +1464,10 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1502,22 +1502,22 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1538,22 +1538,22 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>6</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1573,28 +1573,28 @@
         <v>8</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1615,10 +1615,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1627,7 +1627,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1656,22 +1656,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1692,22 +1692,22 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1733,22 +1733,22 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1769,10 +1769,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1810,22 +1810,22 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1846,7 +1846,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -1858,10 +1858,10 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1887,22 +1887,22 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1923,10 +1923,10 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -1938,7 +1938,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1964,22 +1964,22 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2003,19 +2003,19 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2041,22 +2041,22 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2077,7 +2077,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2086,10 +2086,10 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2112,28 +2112,28 @@
         <v>8</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2157,16 +2157,16 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2195,22 +2195,22 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2231,10 +2231,10 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
@@ -2311,30 +2311,30 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>47.37</v>
+        <v>52.63</v>
       </c>
       <c r="G2">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>21.05</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -2343,30 +2343,30 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>52.63</v>
+        <v>78.95</v>
       </c>
       <c r="G3">
         <v>21.05</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
@@ -2375,30 +2375,30 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>78.95</v>
+      </c>
+      <c r="G4">
+        <v>21.05</v>
+      </c>
+      <c r="H4">
+        <v>7.3</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>84.20999999999999</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>8</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>15.79</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
@@ -2407,19 +2407,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>94.73999999999999</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G5">
-        <v>5.26</v>
+        <v>15.79</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2499,7 +2499,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2528,19 +2528,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920260</v>
+        <v>19330051920314</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>40</v>
@@ -2548,241 +2548,101 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920264</v>
+        <v>20330051920270</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920264</v>
+        <v>19330051920453</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920264</v>
+        <v>20330051920278</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920270</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920270</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920453</v>
-      </c>
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920453</v>
-      </c>
-      <c r="B11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920272</v>
-      </c>
-      <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920278</v>
-      </c>
-      <c r="B13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920282</v>
-      </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2822,16 +2682,16 @@
         <v>20330051920264</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2839,16 +2699,16 @@
         <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2856,16 +2716,16 @@
         <v>20330051920270</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2873,30 +2733,30 @@
         <v>19330051920453</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920260</v>
+        <v>20330051920278</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2904,64 +2764,64 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920272</v>
+        <v>20330051920260</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920278</v>
+        <v>20330051920262</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920282</v>
+        <v>20330051920268</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920262</v>
+        <v>20330051920269</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>89</v>
@@ -2972,13 +2832,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920268</v>
+        <v>20330051920271</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
         <v>90</v>
@@ -2989,13 +2849,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920269</v>
+        <v>20330051920272</v>
       </c>
       <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
         <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
       </c>
       <c r="D12" t="s">
         <v>91</v>
@@ -3006,13 +2866,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920271</v>
+        <v>19220030050208</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
         <v>92</v>
@@ -3023,13 +2883,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19220030050208</v>
+        <v>20330051920273</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -3040,13 +2900,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920273</v>
+        <v>20330051920274</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -3057,13 +2917,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920274</v>
+        <v>20330051920276</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>95</v>
@@ -3074,13 +2934,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920276</v>
+        <v>19330051920238</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
         <v>96</v>
@@ -3091,13 +2951,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920238</v>
+        <v>20330051920279</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
         <v>97</v>
@@ -3108,13 +2968,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920279</v>
+        <v>20330051920282</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
         <v>98</v>
@@ -3128,10 +2988,10 @@
         <v>19330051920425</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
         <v>99</v>
@@ -3147,7 +3007,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3179,71 +3039,71 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920260</v>
+        <v>20330051920278</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920260</v>
+        <v>20330051920278</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920270</v>
+        <v>20330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3251,16 +3111,16 @@
         <v>20330051920270</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>40</v>
@@ -3274,19 +3134,19 @@
         <v>20330051920272</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3294,45 +3154,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920272</v>
+        <v>19220030050208</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>40</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19220030050208</v>
+        <v>20330051920276</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3340,140 +3200,25 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19220030050208</v>
+        <v>19330051920425</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9">
         <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920278</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920278</v>
-      </c>
-      <c r="B11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920268</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920276</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920282</v>
-      </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5APV - Estadisticos 20221.xlsx
+++ b/grupos/5APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="100">
   <si>
     <t>Materia</t>
   </si>
@@ -827,7 +827,7 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -904,7 +904,7 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -978,7 +978,7 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1135,7 +1135,7 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>8</v>
@@ -1212,7 +1212,7 @@
         <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>8</v>
@@ -1248,7 +1248,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1289,7 +1289,7 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>10</v>
@@ -1437,7 +1437,7 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>8</v>
@@ -1585,7 +1585,7 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>8</v>
@@ -1662,7 +1662,7 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>8</v>
@@ -1698,7 +1698,7 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1739,7 +1739,7 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>8</v>
@@ -1775,7 +1775,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -1816,7 +1816,7 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>10</v>
@@ -1852,7 +1852,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -1893,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>7</v>
@@ -1929,7 +1929,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2047,7 +2047,7 @@
         <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>10</v>
@@ -2083,7 +2083,7 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2124,7 +2124,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>10</v>
@@ -2160,7 +2160,7 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2201,7 +2201,7 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>7</v>
@@ -2237,7 +2237,7 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2311,19 +2311,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>52.63</v>
+        <v>57.89</v>
       </c>
       <c r="G2">
-        <v>21.05</v>
+        <v>15.79</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>5</v>
@@ -3007,7 +3007,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3177,47 +3177,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920276</v>
+        <v>19330051920425</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920425</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APV - Estadisticos 20221.xlsx
+++ b/grupos/5APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
   <si>
     <t>Materia</t>
   </si>
@@ -170,22 +170,73 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>GARNICA</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
   </si>
   <si>
     <t>DIAZ</t>
@@ -194,13 +245,40 @@
     <t>TIBURCIO</t>
   </si>
   <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
     <t>JOSE ANTONIO</t>
   </si>
   <si>
-    <t>LEONARDO GAEL</t>
+    <t>IAN URIEL</t>
+  </si>
+  <si>
+    <t>JESUS HUMBERTO</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
   </si>
   <si>
     <t>ELIAS ALONSO</t>
@@ -209,106 +287,28 @@
     <t>JAVIER</t>
   </si>
   <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>KAREN YAZMIN</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
     <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
   </si>
   <si>
     <t>AXEL YAEL</t>
@@ -963,7 +963,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -981,7 +981,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -1017,7 +1017,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1040,7 +1040,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -1058,7 +1058,7 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1094,7 +1094,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>-1</v>
@@ -1348,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -1366,7 +1366,7 @@
         <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>8</v>
@@ -1402,7 +1402,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -1440,7 +1440,7 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -1470,7 +1470,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1952,7 +1952,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>7</v>
@@ -1970,7 +1970,7 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>8</v>
@@ -2006,7 +2006,7 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2311,25 +2311,25 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>57.89</v>
+        <v>63.16</v>
       </c>
       <c r="G2">
-        <v>15.79</v>
+        <v>36.84</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2499,7 +2499,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2528,122 +2528,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920264</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920264</v>
-      </c>
-      <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920270</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920453</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920278</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2682,95 +2582,95 @@
         <v>20330051920264</v>
       </c>
       <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" t="s">
-        <v>55</v>
-      </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920314</v>
+        <v>20330051920260</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920270</v>
+        <v>19330051920314</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920453</v>
+        <v>20330051920262</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920278</v>
+        <v>20330051920268</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920260</v>
+        <v>20330051920269</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
         <v>86</v>
@@ -2781,13 +2681,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920262</v>
+        <v>20330051920270</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
         <v>87</v>
@@ -2798,13 +2698,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920268</v>
+        <v>19330051920453</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
         <v>88</v>
@@ -2815,13 +2715,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920269</v>
+        <v>20330051920271</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
         <v>89</v>
@@ -2832,13 +2732,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920271</v>
+        <v>20330051920272</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
         <v>90</v>
@@ -2849,13 +2749,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920272</v>
+        <v>19220030050208</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
         <v>91</v>
@@ -2866,13 +2766,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19220030050208</v>
+        <v>20330051920273</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
         <v>92</v>
@@ -2883,13 +2783,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920273</v>
+        <v>20330051920274</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -2900,13 +2800,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920274</v>
+        <v>20330051920276</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -2917,13 +2817,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920276</v>
+        <v>19330051920238</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
         <v>95</v>
@@ -2934,13 +2834,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920238</v>
+        <v>20330051920278</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
         <v>96</v>
@@ -2954,10 +2854,10 @@
         <v>20330051920279</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
         <v>97</v>
@@ -2971,10 +2871,10 @@
         <v>20330051920282</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
         <v>98</v>
@@ -2988,10 +2888,10 @@
         <v>19330051920425</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
         <v>99</v>
@@ -3007,7 +2907,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3042,13 +2942,13 @@
         <v>20330051920278</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -3057,7 +2957,7 @@
         <v>40</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3065,13 +2965,13 @@
         <v>20330051920278</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3088,13 +2988,13 @@
         <v>20330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -3108,16 +3008,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920270</v>
+        <v>20330051920272</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -3126,18 +3026,18 @@
         <v>40</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920272</v>
+        <v>19220030050208</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
         <v>91</v>
@@ -3154,47 +3054,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19220030050208</v>
+        <v>19330051920425</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920425</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APV - Estadisticos 20221.xlsx
+++ b/grupos/5APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="100">
   <si>
     <t>Materia</t>
   </si>
@@ -170,109 +170,109 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>GARNICA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>IAN URIEL</t>
+  </si>
+  <si>
     <t>LEONARDO GAEL</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
   </si>
   <si>
     <t>JESUS HUMBERTO</t>
@@ -1043,7 +1043,7 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -1061,7 +1061,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -2442,22 +2442,22 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>94.73999999999999</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2499,7 +2499,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2524,26 +2524,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920264</v>
-      </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2579,30 +2559,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920264</v>
+        <v>20330051920260</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920260</v>
+        <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
         <v>82</v>
@@ -2613,13 +2593,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920314</v>
+        <v>20330051920262</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
         <v>83</v>
@@ -2630,13 +2610,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920262</v>
+        <v>20330051920264</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
         <v>84</v>
@@ -2650,10 +2630,10 @@
         <v>20330051920268</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
         <v>85</v>
@@ -2667,10 +2647,10 @@
         <v>20330051920269</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
         <v>86</v>
@@ -2684,10 +2664,10 @@
         <v>20330051920270</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
         <v>87</v>
@@ -2701,10 +2681,10 @@
         <v>19330051920453</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
         <v>88</v>
@@ -2718,10 +2698,10 @@
         <v>20330051920271</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
         <v>89</v>
@@ -2735,10 +2715,10 @@
         <v>20330051920272</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
         <v>90</v>
@@ -2752,10 +2732,10 @@
         <v>19220030050208</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
         <v>91</v>
@@ -2769,10 +2749,10 @@
         <v>20330051920273</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
         <v>92</v>
@@ -2786,10 +2766,10 @@
         <v>20330051920274</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -2803,10 +2783,10 @@
         <v>20330051920276</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -2820,10 +2800,10 @@
         <v>19330051920238</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
         <v>95</v>
@@ -2837,10 +2817,10 @@
         <v>20330051920278</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
         <v>96</v>
@@ -2854,10 +2834,10 @@
         <v>20330051920279</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>97</v>
@@ -2871,10 +2851,10 @@
         <v>20330051920282</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
         <v>98</v>
@@ -2888,10 +2868,10 @@
         <v>19330051920425</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
         <v>99</v>
@@ -2942,10 +2922,10 @@
         <v>20330051920278</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
         <v>96</v>
@@ -2965,10 +2945,10 @@
         <v>20330051920278</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
         <v>96</v>
@@ -2988,13 +2968,13 @@
         <v>20330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -3011,10 +2991,10 @@
         <v>20330051920272</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
         <v>90</v>
@@ -3034,10 +3014,10 @@
         <v>19220030050208</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
         <v>91</v>
@@ -3057,10 +3037,10 @@
         <v>19330051920425</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
         <v>99</v>

--- a/grupos/5APV - Estadisticos 20221.xlsx
+++ b/grupos/5APV - Estadisticos 20221.xlsx
@@ -146,7 +146,7 @@
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
+    <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>

--- a/grupos/5APV - Estadisticos 20221.xlsx
+++ b/grupos/5APV - Estadisticos 20221.xlsx
@@ -842,7 +842,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -860,7 +860,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -919,7 +919,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -996,7 +996,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1014,7 +1014,7 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1073,7 +1073,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1150,7 +1150,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1168,7 +1168,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1227,7 +1227,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -1304,7 +1304,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1381,7 +1381,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1452,7 +1452,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1523,7 +1523,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1541,7 +1541,7 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1600,7 +1600,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1618,7 +1618,7 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1677,7 +1677,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1695,7 +1695,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1754,7 +1754,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1772,7 +1772,7 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1831,7 +1831,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1908,7 +1908,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -1926,7 +1926,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -1985,7 +1985,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2003,7 +2003,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2062,7 +2062,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2139,7 +2139,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2157,7 +2157,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2216,7 +2216,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2234,7 +2234,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2407,19 +2407,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="G5">
-        <v>15.79</v>
+        <v>10.53</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/5APV - Estadisticos 20221.xlsx
+++ b/grupos/5APV - Estadisticos 20221.xlsx
@@ -848,13 +848,13 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -925,13 +925,13 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1002,13 +1002,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>5</v>
@@ -1079,13 +1079,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1156,13 +1156,13 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1233,13 +1233,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1310,13 +1310,13 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1387,13 +1387,13 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1458,7 +1458,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1473,7 +1473,7 @@
         <v>5</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1529,13 +1529,13 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1606,13 +1606,13 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1683,13 +1683,13 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1760,13 +1760,13 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1837,13 +1837,13 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -1914,13 +1914,13 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -1991,13 +1991,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>6</v>
@@ -2068,13 +2068,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -2145,13 +2145,13 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2222,13 +2222,13 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>5</v>
@@ -2240,7 +2240,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2439,19 +2439,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>94.73999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="G6">
-        <v>5.26</v>
+        <v>10.53</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/5APV - Estadisticos 20221.xlsx
+++ b/grupos/5APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
   <si>
     <t>Materia</t>
   </si>
@@ -143,10 +143,10 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
@@ -839,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>7</v>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -993,7 +993,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>8</v>
@@ -1011,7 +1011,7 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1070,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -1147,7 +1147,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
         <v>7</v>
@@ -1224,7 +1224,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1242,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1319,7 +1319,7 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1378,7 +1378,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>7</v>
@@ -1396,7 +1396,7 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1449,7 +1449,7 @@
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -1520,7 +1520,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>7</v>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>7</v>
@@ -1674,7 +1674,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>7</v>
@@ -1751,7 +1751,7 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>7</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -1905,7 +1905,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -1982,7 +1982,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -2059,7 +2059,7 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>7</v>
@@ -2136,7 +2136,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>7</v>
@@ -2213,7 +2213,7 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2231,7 +2231,7 @@
         <v>9</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -2355,7 +2355,7 @@
         <v>21.05</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2366,7 +2366,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
@@ -2375,19 +2375,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="G4">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2887,7 +2887,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2919,16 +2919,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920278</v>
+        <v>19330051920314</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -2942,22 +2942,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920278</v>
+        <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -2965,16 +2965,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920260</v>
+        <v>20330051920278</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -2988,22 +2988,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920272</v>
+        <v>20330051920278</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3011,16 +3011,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19220030050208</v>
+        <v>20330051920260</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -3034,24 +3034,47 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920425</v>
+        <v>20330051920272</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19220030050208</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APV - Estadisticos 20221.xlsx
+++ b/grupos/5APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="100">
   <si>
     <t>Materia</t>
   </si>
@@ -845,13 +845,13 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -863,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -922,13 +922,13 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -999,13 +999,13 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -1076,13 +1076,13 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>9</v>
@@ -1153,13 +1153,13 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>10</v>
@@ -1171,13 +1171,13 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>8</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1230,13 +1230,13 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -1248,13 +1248,13 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>8</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1307,13 +1307,13 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>9</v>
@@ -1384,13 +1384,13 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>9</v>
@@ -1402,7 +1402,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1455,7 +1455,7 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>5</v>
@@ -1526,13 +1526,13 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <v>10</v>
@@ -1550,7 +1550,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1603,13 +1603,13 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -1621,13 +1621,13 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>8</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1680,13 +1680,13 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>10</v>
@@ -1698,7 +1698,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1757,13 +1757,13 @@
         <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>10</v>
@@ -1834,13 +1834,13 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>10</v>
@@ -1852,7 +1852,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -1911,13 +1911,13 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>10</v>
@@ -1929,13 +1929,13 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>7</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -1988,13 +1988,13 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -2065,13 +2065,13 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -2083,13 +2083,13 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>9</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2142,13 +2142,13 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>9</v>
@@ -2166,7 +2166,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2219,13 +2219,13 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>9</v>
@@ -2237,13 +2237,13 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>7</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2311,16 +2311,16 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>63.16</v>
+        <v>78.95</v>
       </c>
       <c r="G2">
-        <v>36.84</v>
+        <v>21.05</v>
       </c>
       <c r="H2">
         <v>6.8</v>
@@ -2355,7 +2355,7 @@
         <v>21.05</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2887,7 +2887,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3009,75 +3009,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920260</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920272</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19220030050208</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5APV - Estadisticos 20221.xlsx
+++ b/grupos/5APV - Estadisticos 20221.xlsx
@@ -1446,7 +1446,7 @@
         <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1461,7 +1461,7 @@
         <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>5</v>
